--- a/Rawdata/comissoes.xlsx
+++ b/Rawdata/comissoes.xlsx
@@ -463,7 +463,7 @@
     <t>公共房屋事務委員會</t>
   </si>
   <si>
-    <t>澳門鴨涌馬路220號青葱大廈地下L舖</t>
+    <t>澳門沙梨頭北街238號</t>
   </si>
   <si>
     <t>（853）2859 4875</t>
@@ -757,7 +757,7 @@
     <t>Conselho para os Assuntos de Habitação Pública</t>
   </si>
   <si>
-    <t>Estrada do Canal dos Patos, n.º 220, Edifício Cheng Chong, L, R/C, Macau</t>
+    <t>Rua Norte do Patane n.º 238, Macau</t>
   </si>
 </sst>
 </file>
